--- a/docs/test_report_document.xlsx
+++ b/docs/test_report_document.xlsx
@@ -1622,12 +1622,12 @@
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>Light プランのユーザーが症状チェックにアクセスする</t>
+          <t>Light プランのユーザーが症状チェックを実行する</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>アクセス制限エラーが表示される</t>
+          <t>ヒューリスティック（free-local）で重症度と推奨対応が表示される</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="E52" s="18" t="inlineStr">
         <is>
-          <t>アクセス制限エラーが表示される</t>
+          <t>ヒューリスティック（free-local）で重症度と推奨対応が表示される</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>申請/承認/却下/キャンセル・時間バリデーション</t>
+          <t>申請/承認/却下（スタッフ）・キャンセル（オーナー）・時間バリデーション</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>VET/STAFF/ADMIN のみ CRUD</t>
+          <t>SUPER/VET/STAFF のみ CRUD</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr"/>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>OpenAI 呼び出し / フォールバック / プラン制限</t>
+          <t>OpenAI 呼び出し / フォールバック（Light は free-local）</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr"/>

--- a/docs/test_report_document.xlsx
+++ b/docs/test_report_document.xlsx
@@ -3360,13 +3360,93 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">テストマトリックス（Pet Life Plus）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参照元: docs/09-test-report.html, docs/test-checklist.md, docs/test-matrix.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">目的: 機能・ロール・品質観点・実行条件の対応関係を一覧化し、テストの抜け漏れを防ぐ。</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">テストマトリックス（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Pet Life Plus</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">参照元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/09-test-report.html, docs/test-checklist.md, docs/test-matrix.md</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">機能・ロール・品質観点・実行条件の対応関係を一覧化し、テストの抜け漏れを防ぐ。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">目的</t>
@@ -3375,19 +3455,76 @@
     <t xml:space="preserve">内容</t>
   </si>
   <si>
-    <t xml:space="preserve">目的1</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">テストケースの抜け漏れを機能横断で確認する</t>
   </si>
   <si>
-    <t xml:space="preserve">目的2</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ロール差異、外部連携、フォールバック、異常系の網羅状況を見える化する</t>
   </si>
   <si>
-    <t xml:space="preserve">目的3</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">実施前に、どの環境・どのアカウントで何を確認するかを固める</t>
@@ -3420,7 +3557,36 @@
     <t xml:space="preserve">対象外</t>
   </si>
   <si>
-    <t xml:space="preserve">機能 × ロール</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">機能 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ロール</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">機能</t>
@@ -3444,22 +3610,186 @@
     <t xml:space="preserve">USER Premium</t>
   </si>
   <si>
-    <t xml:space="preserve">関連TC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-001〜004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-005〜007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-008〜013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-014〜017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-018〜020</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">関連</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">004</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">007</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-008</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">013</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-014</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">017</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-018</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">020</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">診療予約申請</t>
@@ -3480,10 +3810,58 @@
     <t xml:space="preserve">TC-027b</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-028〜029b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI症状チェック</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-028</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">029b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">症状チェック</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-032,033</t>
@@ -3492,10 +3870,68 @@
     <t xml:space="preserve">チャットボット相談</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-034,035,065〜067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-036〜039</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-034,035,065</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">067</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-036</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">039</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">通知・既読管理</t>
@@ -3510,10 +3946,58 @@
     <t xml:space="preserve">TC-043,044</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-045〜048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoom オンライン診療</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-045</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">048</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">オンライン診療</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-050,051</t>
@@ -3525,7 +4009,36 @@
     <t xml:space="preserve">請求・決済管理</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-059〜063</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-059</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">063</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">診療情報印刷</t>
@@ -3534,7 +4047,36 @@
     <t xml:space="preserve">TC-064</t>
   </si>
   <si>
-    <t xml:space="preserve">機能 × 品質観点</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">機能 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">品質観点</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">機能群</t>
@@ -3552,37 +4094,329 @@
     <t xml:space="preserve">認証・共通</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-001〜007,030,031,056〜058</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">007,030,031,056</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">058</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ユーザー・ペット管理</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-008〜020,042〜044,064</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-008</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">020,042</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">044,064</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">予約・診療</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-021〜029b,040,041,052,053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI・チャット</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-032〜035,045〜051,065〜067</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">029b,040,041,052,053</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・チャット</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-032</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">035,045</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">051,065</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">067</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">管理・請求</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-054,055,059〜063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">機能 × 実行環境</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCブラウザ</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-054,055,059</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">063</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">機能 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">実行環境</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PC</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ブラウザ</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">スマホブラウザ</t>
@@ -3600,13 +4434,61 @@
     <t xml:space="preserve">Zoom</t>
   </si>
   <si>
-    <t xml:space="preserve">APIキー未設定確認</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">キー未設定確認</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ログイン・ダッシュボード</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-001〜007</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">007</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ユーザー・ペット・健康記録</t>
@@ -3618,22 +4500,137 @@
     <t xml:space="preserve">パスワード再設定</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-056〜058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LINE連携機能</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slack連携機能</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoomオンライン診療</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-056</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">058</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">連携機能</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Slack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">連携機能</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">オンライン診療</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">請求・決済・印刷</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-059〜064</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-059</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">064</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ロール別の重点確認観点</t>
@@ -3651,10 +4648,78 @@
     <t xml:space="preserve">管理機能への到達性</t>
   </si>
   <si>
-    <t xml:space="preserve">KPI、予約枠、お知らせ、統計、請求、請求書表示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-005,027,029b,052〜055,059〜063</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">、予約枠、お知らせ、統計、請求、請求書表示</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-005,027,029b,052</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">055,059</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">063</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">予約処理権限</t>
@@ -3678,7 +4743,26 @@
     <t xml:space="preserve">制限付き利用</t>
   </si>
   <si>
-    <t xml:space="preserve">AI症状チェックのフォールバック、チャットボット可、予約不可</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">症状チェックのフォールバック、チャットボット可、予約不可</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-006,033,042,065,067</t>
@@ -3687,19 +4771,135 @@
     <t xml:space="preserve">標準機能利用</t>
   </si>
   <si>
-    <t xml:space="preserve">予約申請、AI症状チェック、契約表示、パスワード変更</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-021,032,042〜044</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">予約申請、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">症状チェック、契約表示、パスワード変更</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-021,032,042</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">044</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">上位機能利用</t>
   </si>
   <si>
-    <t xml:space="preserve">標準機能に加え Zoom オンライン診療可</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-021,032,042〜044,050</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">標準機能に加え </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">オンライン診療可</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TC-021,032,042</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">044,050</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">未実施になりやすい観点</t>
@@ -3714,7 +4914,26 @@
     <t xml:space="preserve">代替記録方法</t>
   </si>
   <si>
-    <t xml:space="preserve">SendGrid メール送信</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SendGrid </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">メール送信</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">検証用メール環境が必要</t>
@@ -3729,28 +4948,201 @@
     <t xml:space="preserve">フォロワーとチャネル設定が必要</t>
   </si>
   <si>
-    <t xml:space="preserve">LINE 管理画面ログ、受信端末キャプチャ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slack DM 応答</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slack App と DM 先が必要</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slack スクリーンショット、アプリログ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoom 予約導線</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premium アカウントと Zoom 設定が必要</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">管理画面ログ、受信端末キャプチャ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Slack DM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">応答</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Slack App </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">と </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">先が必要</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Slack </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">スクリーンショット、アプリログ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">予約導線</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Premium </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">アカウントと </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">設定が必要</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">予約詳細画面、通知、発行リンク確認</t>
   </si>
   <si>
-    <t xml:space="preserve">API キー未設定フォールバック</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">キー未設定フォールバック</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">環境変数切替が必要</t>
@@ -3774,7 +5166,36 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">基本 CRUD（ユーザー、ペット、健康記録）</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">基本 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（ユーザー、ペット、健康記録）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">3</t>
@@ -3786,13 +5207,121 @@
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">AI症状チェック、チャットボット</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">症状チェック、チャットボット</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">外部連携（LINE、Slack、Zoom、SendGrid）</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">外部連携（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Slack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zoom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SendGrid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">6</t>
@@ -3804,19 +5333,154 @@
     <t xml:space="preserve">補足</t>
   </si>
   <si>
-    <t xml:space="preserve">補足1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">△ は条件付き対応。STAFF や VET は機能の一部のみ実行できるケースがある。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">補足2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">実際の判定記録は docs/test-checklist.md に残す。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">補足3</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">補足</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△ は条件付き対応。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STAFF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">や </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VET </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">は機能の一部のみ実行できるケースがある。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">補足</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">実際の判定記録は </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docs/test-checklist.md </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">に残す。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">補足</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">追加機能が増えた場合は、先に本マトリックスへ観点追加し、その後チェックリストへ具体項目を足す。</t>
@@ -3829,7 +5493,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3928,6 +5592,14 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="游ゴシック体"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック体"/>
       <family val="2"/>
       <charset val="1"/>
@@ -4089,104 +5761,116 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4596,962 +6280,962 @@
   <dimension ref="A1:E56"/>
   <sheetFormatPr defaultColWidth="8.4453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="13" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="14" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="11" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="14" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="11" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="11" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="14" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="14" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="11" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="14" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="11" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="14" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="11" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="11" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="14" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="11" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="14" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="14" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="14" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="14" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="11" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="14" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="10" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="E49" s="14" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="11" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="14" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="11" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="14" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="11" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="E55" s="13" t="s">
+      <c r="E55" s="14" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="11" t="s">
         <v>204</v>
       </c>
     </row>
@@ -5585,334 +7269,334 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="11" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="13"/>
+      <c r="E3" s="14" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="11" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="14" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="11" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13" t="s">
+      <c r="D7" s="13"/>
+      <c r="E7" s="14" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="11" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13" t="s">
+      <c r="D9" s="13"/>
+      <c r="E9" s="14" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="10"/>
+      <c r="E10" s="11" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13" t="s">
+      <c r="D11" s="13"/>
+      <c r="E11" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>244</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="11" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13" t="s">
+      <c r="D13" s="13"/>
+      <c r="E13" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10" t="s">
+      <c r="D14" s="10"/>
+      <c r="E14" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="13"/>
+      <c r="E15" s="14" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="10" t="s">
+      <c r="D16" s="10"/>
+      <c r="E16" s="11" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13" t="s">
+      <c r="D17" s="13"/>
+      <c r="E17" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="10" t="s">
+      <c r="D18" s="10"/>
+      <c r="E18" s="11" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13" t="s">
+      <c r="D19" s="13"/>
+      <c r="E19" s="14" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10" t="s">
+      <c r="D20" s="10"/>
+      <c r="E20" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13" t="s">
+      <c r="D21" s="13"/>
+      <c r="E21" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10" t="s">
+      <c r="D22" s="10"/>
+      <c r="E22" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5944,13 +7628,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>279</v>
       </c>
     </row>
@@ -6070,12 +7754,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I94"/>
-  <sheetFormatPr defaultColWidth="8.4453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="18" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="18" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="18" width="24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="18" width="8.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6131,7 +7815,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
         <v>302</v>
       </c>
@@ -6139,7 +7823,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="28.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
         <v>304</v>
       </c>
@@ -6147,7 +7831,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="28.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
         <v>306</v>
       </c>
@@ -6186,7 +7870,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="24" t="s">
         <v>315</v>
       </c>
       <c r="B15" s="23" t="s">
@@ -6209,22 +7893,22 @@
       <c r="A18" s="22" t="s">
         <v>318</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="25" t="s">
         <v>319</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="25" t="s">
         <v>320</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="25" t="s">
         <v>321</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="25" t="s">
         <v>323</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="25" t="s">
         <v>324</v>
       </c>
       <c r="H18" s="22" t="s">
@@ -6235,25 +7919,25 @@
       <c r="A19" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H19" s="23" t="s">
+      <c r="B19" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H19" s="24" t="s">
         <v>326</v>
       </c>
     </row>
@@ -6261,25 +7945,25 @@
       <c r="A20" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H20" s="23" t="s">
+      <c r="B20" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H20" s="24" t="s">
         <v>327</v>
       </c>
     </row>
@@ -6287,25 +7971,25 @@
       <c r="A21" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="B21" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C21" s="24" t="s">
+      <c r="B21" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="F21" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="24" t="s">
         <v>328</v>
       </c>
     </row>
@@ -6313,25 +7997,25 @@
       <c r="A22" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H22" s="23" t="s">
+      <c r="B22" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H22" s="24" t="s">
         <v>329</v>
       </c>
     </row>
@@ -6339,25 +8023,25 @@
       <c r="A23" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H23" s="23" t="s">
+      <c r="B23" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H23" s="24" t="s">
         <v>330</v>
       </c>
     </row>
@@ -6365,25 +8049,25 @@
       <c r="A24" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F24" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H24" s="23" t="s">
+      <c r="F24" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H24" s="24" t="s">
         <v>332</v>
       </c>
     </row>
@@ -6391,25 +8075,25 @@
       <c r="A25" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D25" s="24" t="s">
+      <c r="C25" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D25" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G25" s="24" t="s">
+      <c r="G25" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H25" s="23" t="s">
+      <c r="H25" s="24" t="s">
         <v>334</v>
       </c>
     </row>
@@ -6417,25 +8101,25 @@
       <c r="A26" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="F26" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H26" s="23" t="s">
+      <c r="F26" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H26" s="24" t="s">
         <v>336</v>
       </c>
     </row>
@@ -6443,51 +8127,51 @@
       <c r="A27" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E27" s="24" t="s">
+      <c r="C27" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E27" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="24" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="24" t="s">
         <v>338</v>
       </c>
-      <c r="B28" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G28" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H28" s="23" t="s">
+      <c r="B28" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H28" s="24" t="s">
         <v>339</v>
       </c>
     </row>
@@ -6495,25 +8179,25 @@
       <c r="A29" s="23" t="s">
         <v>340</v>
       </c>
-      <c r="B29" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F29" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H29" s="23" t="s">
+      <c r="B29" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H29" s="24" t="s">
         <v>341</v>
       </c>
     </row>
@@ -6521,25 +8205,25 @@
       <c r="A30" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="B30" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F30" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G30" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H30" s="23" t="s">
+      <c r="B30" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H30" s="24" t="s">
         <v>342</v>
       </c>
     </row>
@@ -6547,25 +8231,25 @@
       <c r="A31" s="23" t="s">
         <v>343</v>
       </c>
-      <c r="B31" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F31" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G31" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H31" s="23" t="s">
+      <c r="B31" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G31" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H31" s="24" t="s">
         <v>344</v>
       </c>
     </row>
@@ -6573,25 +8257,25 @@
       <c r="A32" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E32" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F32" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G32" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H32" s="23" t="s">
+      <c r="E32" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H32" s="24" t="s">
         <v>156</v>
       </c>
     </row>
@@ -6599,103 +8283,103 @@
       <c r="A33" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="B33" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F33" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G33" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H33" s="23" t="s">
+      <c r="B33" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G33" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H33" s="24" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="B34" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C34" s="24" t="s">
+      <c r="B34" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C34" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="G34" s="24" t="s">
+      <c r="G34" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="24" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="24" t="s">
         <v>260</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="G35" s="24" t="s">
+      <c r="G35" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="H35" s="23" t="s">
+      <c r="H35" s="24" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="24" t="s">
         <v>348</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="C36" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D36" s="24" t="s">
+      <c r="C36" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D36" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G36" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H36" s="23" t="s">
+      <c r="G36" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H36" s="24" t="s">
         <v>349</v>
       </c>
     </row>
@@ -6703,25 +8387,25 @@
       <c r="A37" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="B37" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D37" s="24" t="s">
+      <c r="B37" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D37" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G37" s="24" t="s">
+      <c r="G37" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H37" s="23" t="s">
+      <c r="H37" s="24" t="s">
         <v>350</v>
       </c>
     </row>
@@ -6729,25 +8413,25 @@
       <c r="A38" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="B38" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C38" s="24" t="s">
+      <c r="B38" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C38" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D38" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G38" s="24" t="s">
+      <c r="G38" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H38" s="23" t="s">
+      <c r="H38" s="24" t="s">
         <v>197</v>
       </c>
     </row>
@@ -6755,25 +8439,25 @@
       <c r="A39" s="23" t="s">
         <v>275</v>
       </c>
-      <c r="B39" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C39" s="24" t="s">
+      <c r="B39" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C39" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="D39" s="24" t="s">
+      <c r="D39" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G39" s="24" t="s">
+      <c r="G39" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H39" s="23" t="s">
+      <c r="H39" s="24" t="s">
         <v>201</v>
       </c>
     </row>
@@ -6781,25 +8465,25 @@
       <c r="A40" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="B40" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C40" s="24" t="s">
+      <c r="B40" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C40" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E40" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G40" s="24" t="s">
+      <c r="G40" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H40" s="23" t="s">
+      <c r="H40" s="24" t="s">
         <v>352</v>
       </c>
     </row>
@@ -6807,25 +8491,25 @@
       <c r="A41" s="23" t="s">
         <v>353</v>
       </c>
-      <c r="B41" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E41" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F41" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G41" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H41" s="23" t="s">
+      <c r="B41" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C41" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H41" s="24" t="s">
         <v>354</v>
       </c>
     </row>
@@ -6871,25 +8555,25 @@
       <c r="A45" s="23" t="s">
         <v>360</v>
       </c>
-      <c r="B45" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D45" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E45" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F45" s="24" t="s">
+      <c r="B45" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E45" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F45" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="G45" s="24" t="s">
+      <c r="G45" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H45" s="23" t="s">
+      <c r="H45" s="24" t="s">
         <v>361</v>
       </c>
     </row>
@@ -6897,25 +8581,25 @@
       <c r="A46" s="23" t="s">
         <v>362</v>
       </c>
-      <c r="B46" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E46" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F46" s="24" t="s">
+      <c r="B46" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F46" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G46" s="24" t="s">
+      <c r="G46" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H46" s="23" t="s">
+      <c r="H46" s="24" t="s">
         <v>363</v>
       </c>
     </row>
@@ -6923,51 +8607,51 @@
       <c r="A47" s="23" t="s">
         <v>364</v>
       </c>
-      <c r="B47" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D47" s="24" t="s">
+      <c r="B47" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D47" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E47" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F47" s="24" t="s">
+      <c r="E47" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F47" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="G47" s="24" t="s">
+      <c r="G47" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H47" s="23" t="s">
+      <c r="H47" s="24" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="24" t="s">
         <v>366</v>
       </c>
-      <c r="B48" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C48" s="24" t="s">
+      <c r="B48" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C48" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D48" s="24" t="s">
+      <c r="D48" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E48" s="24" t="s">
+      <c r="E48" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F48" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G48" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H48" s="23" t="s">
+      <c r="F48" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G48" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H48" s="24" t="s">
         <v>367</v>
       </c>
     </row>
@@ -6975,25 +8659,25 @@
       <c r="A49" s="23" t="s">
         <v>368</v>
       </c>
-      <c r="B49" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C49" s="24" t="s">
+      <c r="B49" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C49" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D49" s="24" t="s">
+      <c r="D49" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E49" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F49" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G49" s="24" t="s">
+      <c r="E49" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G49" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="H49" s="23" t="s">
+      <c r="H49" s="24" t="s">
         <v>369</v>
       </c>
     </row>
@@ -7014,7 +8698,7 @@
       <c r="A52" s="22" t="s">
         <v>356</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="B52" s="25" t="s">
         <v>371</v>
       </c>
       <c r="C52" s="22" t="s">
@@ -7023,16 +8707,16 @@
       <c r="D52" s="22" t="s">
         <v>373</v>
       </c>
-      <c r="E52" s="22" t="s">
+      <c r="E52" s="25" t="s">
         <v>374</v>
       </c>
-      <c r="F52" s="22" t="s">
+      <c r="F52" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="G52" s="22" t="s">
+      <c r="G52" s="25" t="s">
         <v>376</v>
       </c>
-      <c r="H52" s="22" t="s">
+      <c r="H52" s="25" t="s">
         <v>377</v>
       </c>
       <c r="I52" s="22" t="s">
@@ -7043,28 +8727,28 @@
       <c r="A53" s="23" t="s">
         <v>378</v>
       </c>
-      <c r="B53" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C53" s="24" t="s">
+      <c r="B53" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C53" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D53" s="24" t="s">
+      <c r="D53" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="E53" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F53" s="24" t="s">
+      <c r="F53" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G53" s="24" t="s">
+      <c r="G53" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H53" s="24" t="s">
+      <c r="H53" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="I53" s="23" t="s">
+      <c r="I53" s="24" t="s">
         <v>379</v>
       </c>
     </row>
@@ -7072,28 +8756,28 @@
       <c r="A54" s="23" t="s">
         <v>380</v>
       </c>
-      <c r="B54" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C54" s="24" t="s">
+      <c r="B54" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C54" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D54" s="24" t="s">
+      <c r="D54" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E54" s="24" t="s">
+      <c r="E54" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F54" s="24" t="s">
+      <c r="F54" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G54" s="24" t="s">
+      <c r="G54" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H54" s="24" t="s">
+      <c r="H54" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="I54" s="23" t="s">
+      <c r="I54" s="24" t="s">
         <v>363</v>
       </c>
     </row>
@@ -7101,57 +8785,57 @@
       <c r="A55" s="23" t="s">
         <v>381</v>
       </c>
-      <c r="B55" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C55" s="24" t="s">
+      <c r="B55" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="E55" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F55" s="24" t="s">
+      <c r="F55" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G55" s="24" t="s">
+      <c r="G55" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="H55" s="24" t="s">
+      <c r="H55" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="I55" s="23" t="s">
+      <c r="I55" s="24" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="24" t="s">
         <v>338</v>
       </c>
-      <c r="B56" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D56" s="24" t="s">
+      <c r="B56" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D56" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="E56" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F56" s="24" t="s">
+      <c r="F56" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G56" s="24" t="s">
+      <c r="G56" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H56" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I56" s="23" t="s">
+      <c r="H56" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="I56" s="24" t="s">
         <v>339</v>
       </c>
     </row>
@@ -7159,28 +8843,28 @@
       <c r="A57" s="23" t="s">
         <v>340</v>
       </c>
-      <c r="B57" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D57" s="24" t="s">
+      <c r="B57" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D57" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="E57" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F57" s="24" t="s">
+      <c r="F57" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G57" s="24" t="s">
+      <c r="G57" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H57" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I57" s="23" t="s">
+      <c r="H57" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="I57" s="24" t="s">
         <v>341</v>
       </c>
     </row>
@@ -7188,115 +8872,115 @@
       <c r="A58" s="23" t="s">
         <v>382</v>
       </c>
-      <c r="B58" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C58" s="24" t="s">
+      <c r="B58" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C58" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D58" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E58" s="24" t="s">
+      <c r="D58" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E58" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F58" s="24" t="s">
+      <c r="F58" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G58" s="24" t="s">
+      <c r="G58" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H58" s="24" t="s">
+      <c r="H58" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="I58" s="23" t="s">
+      <c r="I58" s="24" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="24" t="s">
         <v>384</v>
       </c>
-      <c r="B59" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="D59" s="24" t="s">
+      <c r="B59" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="D59" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E59" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F59" s="24" t="s">
+      <c r="E59" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F59" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G59" s="24" t="s">
+      <c r="G59" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H59" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="I59" s="23" t="s">
+      <c r="H59" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="I59" s="24" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="24" t="s">
         <v>385</v>
       </c>
-      <c r="B60" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C60" s="24" t="s">
+      <c r="B60" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C60" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D60" s="24" t="s">
+      <c r="D60" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E60" s="24" t="s">
+      <c r="E60" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F60" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="G60" s="24" t="s">
+      <c r="F60" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G60" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H60" s="24" t="s">
+      <c r="H60" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="I60" s="23" t="s">
+      <c r="I60" s="24" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="24" t="s">
         <v>386</v>
       </c>
-      <c r="B61" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C61" s="24" t="s">
+      <c r="B61" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C61" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D61" s="24" t="s">
+      <c r="D61" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E61" s="24" t="s">
+      <c r="E61" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="F61" s="24" t="s">
+      <c r="F61" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G61" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="H61" s="24" t="s">
+      <c r="G61" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="H61" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="I61" s="23" t="s">
+      <c r="I61" s="24" t="s">
         <v>349</v>
       </c>
     </row>
@@ -7304,28 +8988,28 @@
       <c r="A62" s="23" t="s">
         <v>387</v>
       </c>
-      <c r="B62" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="C62" s="24" t="s">
+      <c r="B62" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C62" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="D62" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="E62" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="F62" s="24" t="s">
+      <c r="D62" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="F62" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G62" s="24" t="s">
+      <c r="G62" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="H62" s="24" t="s">
+      <c r="H62" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="I62" s="23" t="s">
+      <c r="I62" s="24" t="s">
         <v>388</v>
       </c>
     </row>
@@ -7352,86 +9036,86 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="24" t="s">
         <v>319</v>
       </c>
-      <c r="B66" s="24" t="s">
+      <c r="B66" s="26" t="s">
         <v>393</v>
       </c>
-      <c r="C66" s="24" t="s">
+      <c r="C66" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="D66" s="23" t="s">
+      <c r="D66" s="24" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="23" t="s">
+    <row r="67" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="24" t="s">
         <v>320</v>
       </c>
-      <c r="B67" s="24" t="s">
+      <c r="B67" s="26" t="s">
         <v>396</v>
       </c>
-      <c r="C67" s="24" t="s">
+      <c r="C67" s="26" t="s">
         <v>397</v>
       </c>
-      <c r="D67" s="23" t="s">
+      <c r="D67" s="24" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="23" t="s">
+    <row r="68" customFormat="false" ht="28.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="24" t="s">
         <v>321</v>
       </c>
-      <c r="B68" s="24" t="s">
+      <c r="B68" s="26" t="s">
         <v>399</v>
       </c>
-      <c r="C68" s="24" t="s">
+      <c r="C68" s="26" t="s">
         <v>400</v>
       </c>
-      <c r="D68" s="23" t="s">
+      <c r="D68" s="24" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="23" t="s">
+    <row r="69" customFormat="false" ht="29.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="24" t="s">
         <v>322</v>
       </c>
-      <c r="B69" s="24" t="s">
+      <c r="B69" s="26" t="s">
         <v>402</v>
       </c>
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="27" t="s">
         <v>403</v>
       </c>
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="24" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="23" t="s">
+    <row r="70" customFormat="false" ht="29.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="26" t="s">
         <v>405</v>
       </c>
-      <c r="C70" s="24" t="s">
+      <c r="C70" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="D70" s="23" t="s">
+      <c r="D70" s="24" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="23" t="s">
+    <row r="71" customFormat="false" ht="20.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="24" t="s">
         <v>324</v>
       </c>
-      <c r="B71" s="24" t="s">
+      <c r="B71" s="26" t="s">
         <v>408</v>
       </c>
-      <c r="C71" s="24" t="s">
+      <c r="C71" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D71" s="23" t="s">
+      <c r="D71" s="24" t="s">
         <v>410</v>
       </c>
     </row>
@@ -7453,55 +9137,55 @@
         <v>414</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="23" t="s">
+    <row r="75" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="B75" s="24" t="s">
+      <c r="B75" s="26" t="s">
         <v>416</v>
       </c>
       <c r="C75" s="23" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="23" t="s">
+    <row r="76" customFormat="false" ht="20.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="B76" s="24" t="s">
+      <c r="B76" s="26" t="s">
         <v>419</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="24" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="23" t="s">
+    <row r="77" customFormat="false" ht="20.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="24" t="s">
         <v>421</v>
       </c>
-      <c r="B77" s="24" t="s">
+      <c r="B77" s="27" t="s">
         <v>422</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="24" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="23" t="s">
+      <c r="A78" s="24" t="s">
         <v>424</v>
       </c>
-      <c r="B78" s="24" t="s">
+      <c r="B78" s="27" t="s">
         <v>425</v>
       </c>
       <c r="C78" s="23" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="23" t="s">
+    <row r="79" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="24" t="s">
         <v>427</v>
       </c>
-      <c r="B79" s="24" t="s">
+      <c r="B79" s="26" t="s">
         <v>428</v>
       </c>
       <c r="C79" s="23" t="s">
@@ -7522,16 +9206,16 @@
         <v>301</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="23" t="s">
+    <row r="83" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="24" t="s">
         <v>432</v>
       </c>
       <c r="B83" s="23" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="23" t="s">
+    <row r="84" customFormat="false" ht="20.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="24" t="s">
         <v>434</v>
       </c>
       <c r="B84" s="23" t="s">
@@ -7539,23 +9223,23 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="23" t="s">
+      <c r="A85" s="24" t="s">
         <v>436</v>
       </c>
       <c r="B85" s="23" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="23" t="s">
+    <row r="86" customFormat="false" ht="20.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="24" t="s">
         <v>438</v>
       </c>
-      <c r="B86" s="23" t="s">
+      <c r="B86" s="24" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="22.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="23" t="s">
+      <c r="A87" s="24" t="s">
         <v>440</v>
       </c>
       <c r="B87" s="23" t="s">
@@ -7563,7 +9247,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="23" t="s">
+      <c r="A88" s="24" t="s">
         <v>442</v>
       </c>
       <c r="B88" s="23" t="s">
@@ -7584,7 +9268,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="31.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="23" t="s">
         <v>445</v>
       </c>
@@ -7592,7 +9276,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="33.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="29.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="23" t="s">
         <v>447</v>
       </c>
@@ -7600,7 +9284,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="43.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="37.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="23" t="s">
         <v>449</v>
       </c>

--- a/docs/test_report_document.xlsx
+++ b/docs/test_report_document.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="454">
   <si>
     <r>
       <rPr>
@@ -274,7 +274,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026-05-29</t>
+      <t xml:space="preserve">2026-06-29</t>
     </r>
     <r>
       <rPr>
@@ -294,7 +294,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026-06-01</t>
+      <t xml:space="preserve">2026-06-30</t>
     </r>
     <r>
       <rPr>
@@ -795,7 +795,25 @@
     <t xml:space="preserve">ペット名未入力で登録する</t>
   </si>
   <si>
-    <t xml:space="preserve">必須エラーが表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">必須エラーが表示される
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">空白は許可されていません</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-017</t>
@@ -825,7 +843,25 @@
     <t xml:space="preserve">体重に文字列を入力する</t>
   </si>
   <si>
-    <t xml:space="preserve">数値形式エラーが表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">数値形式エラーが表示される
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">エラー表示なし。データとして入力無効</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-020</t>
@@ -986,7 +1022,25 @@
     <t xml:space="preserve">過去日時で予約申請する</t>
   </si>
   <si>
-    <t xml:space="preserve">「未来日時を指定してください」エラーが表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">「未来日時を指定してください」エラーが表示される
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">エラー表示なし。選択可能にならないので、問題なし</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-026</t>
@@ -1021,7 +1075,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">「診療受付時間外」エラーが表示される</t>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">「診療受付時間外」エラーが表示される
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">時間枠の選択制のため、端数指示はできない</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TC-027</t>
@@ -1454,1010 +1526,716 @@
     <t xml:space="preserve">ユーザー数・ペット数・予約数等の集計値が表示される</t>
   </si>
   <si>
+    <t xml:space="preserve">機能ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">機能名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">テスト観点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">備考（制約・前提）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ログイン認証</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCrypt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">認証・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Spring Security form login</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">正常系・異常系・セキュリティ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダッシュボード</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ロール別</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">表示（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ADMIN/VET/STAFF/USER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">正常系・境界値</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ユーザー管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRUD・プラン変更・連携ステータスアイコン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ペット管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRUD・生年月日バリデーション</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正常系・異常系・境界値</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">健康記録管理</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">体重・記録日 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・ソフトデリート</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">F-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">診療予約</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">申請</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">承認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">却下（スタッフ）・キャンセル（オーナー）・時間バリデーション</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">F-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">診療記録</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SUPER/VET/STAFF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">のみ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRUD</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">正常系・セキュリティ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力バリデーション</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必須・メール形式・数値・日付 チェック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">正常系・異常系</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI症状チェック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenAI 呼び出し / フォールバック（Light は free-local）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相談チャットボット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マルチターン対話・即時受診判定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カレンダー</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">手動シール・自動シール・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VET/STAFF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">サイドバー</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">F-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通知・リマインダー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通知一覧・既読処理・スケジュールリマインダー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サブスクリプション</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">契約プラン確認（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">USER / ADMIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">全件）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">F-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスワード変更</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">現在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">照合・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCrypt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">再ハッシュ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">F-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINE Bot / Broadcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webhook 受信・Reply / Broadcast 送信</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slack Bot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webhook 受信・Reply 送信</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoom オンライン診療</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium プラン限定・Zoom リンク発行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予約枠管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADMIN/STAFF による枠登録・カレンダー連携</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">お知らせ管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADMIN/STAFF 作成・全ユーザー表示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">連携ステータスアイコン</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ユーザー管理画面 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE/Slack/Zoom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Microsoft Sans Serif"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">チップ表示</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">F-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サービス統計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADMIN 専用 集計ダッシュボード</t>
+  </si>
+  <si>
+    <t xml:space="preserve">区分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">備考</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ブラウザ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Google Chrome</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（最新版）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Microsoft Edge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（最新版）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mozilla Firefox</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（最新版）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Safari</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（最新版）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">iPhone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">macOS 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iOS 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Android 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Android</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期間</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-05-18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">～ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-06-29</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">予備日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 2026-06-30</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="10"/>
+        <sz val="9"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="游ゴシック体"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">機能</t>
+      <t xml:space="preserve">テストマトリックス（</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="10"/>
+        <sz val="9"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ID</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">機能名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テスト観点</t>
-  </si>
-  <si>
-    <t xml:space="preserve">備考（制約・前提）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ログイン認証</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BCrypt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">認証・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Spring Security form login</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">正常系・異常系・セキュリティ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダッシュボード</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ロール別</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">KPI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">表示（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ADMIN/VET/STAFF/USER</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">正常系・境界値</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ユーザー管理</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CRUD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">・プラン変更・連携ステータスアイコン</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ペット管理</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CRUD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">・生年月日バリデーション</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">正常系・異常系・境界値</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">健康記録管理</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">体重・記録日 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CRUD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">・ソフトデリート</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">診療予約</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">申請</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">承認</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">却下（スタッフ）・キャンセル（オーナー）・時間バリデーション</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">診療記録</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SUPER/VET/STAFF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">のみ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CRUD</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">正常系・セキュリティ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">入力バリデーション</t>
-  </si>
-  <si>
-    <t xml:space="preserve">必須・メール形式・数値・日付 チェック</t>
-  </si>
-  <si>
-    <t xml:space="preserve">正常系・異常系</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-009</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">症状チェック</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">呼び出し </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">フォールバック（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Light </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">は </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">free-local</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相談チャットボット</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マルチターン対話・即時受診判定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カレンダー</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">手動シール・自動シール・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">VET/STAFF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">サイドバー</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通知・リマインダー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通知一覧・既読処理・スケジュールリマインダー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">サブスクリプション</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">契約プラン確認（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">USER / ADMIN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">全件）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パスワード変更</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">現在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">照合・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BCrypt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">再ハッシュ</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LINE Bot / Broadcast</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Webhook </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">受信・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Reply / Broadcast </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">送信</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slack Bot</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Webhook </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">受信・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Reply </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">送信</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-017</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Zoom </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">オンライン診療</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Premium </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">プラン限定・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Zoom </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">リンク発行</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予約枠管理</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ADMIN/STAFF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">による枠登録・カレンダー連携</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">お知らせ管理</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ADMIN/STAFF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">作成・全ユーザー表示</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">連携ステータスアイコン</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ユーザー管理画面 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LINE/Slack/Zoom </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">チップ表示</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F-021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">サービス統計</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Cambria"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ADMIN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">専用 集計ダッシュボード</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">区分</t>
-  </si>
-  <si>
-    <t xml:space="preserve">項目</t>
-  </si>
-  <si>
-    <t xml:space="preserve">備考</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ブラウザ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Google Chrome</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">（最新版）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">PC</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Microsoft Edge</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">（最新版）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Mozilla Firefox</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">（最新版）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Safari</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">（最新版）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">iPhone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows 11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">macOS 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iOS 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Android 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Android</t>
-  </si>
-  <si>
-    <t xml:space="preserve">期間</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-05-18 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">～ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-05-29</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">予備日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 2026-06-01</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Pet Life Plus</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -2467,227 +2245,208 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">テストマトリックス（</t>
-    </r>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">参照元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: docs/09-test-report.html, docs/test-checklist.md, docs/test-matrix.md</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">機能・ロール・品質観点・実行条件の対応関係を一覧化し、テストの抜け漏れを防ぐ。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">目的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内容</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">テストケースの抜け漏れを機能横断で確認する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ロール差異、外部連携、フォールバック、異常系の網羅状況を見える化する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">目的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">実施前に、どの環境・どのアカウントで何を確認するかを固める</t>
+  </si>
+  <si>
+    <t xml:space="preserve">判定記号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意味</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○</t>
+  </si>
+  <si>
+    <t xml:space="preserve">対応あり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">条件付きで対応あり</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">対象外</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Pet Life Plus</t>
+        <rFont val="游ゴシック体"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">機能 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
         <rFont val="游ゴシック体"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">参照元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: docs/09-test-report.html, docs/test-checklist.md, docs/test-matrix.md</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">目的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">機能・ロール・品質観点・実行条件の対応関係を一覧化し、テストの抜け漏れを防ぐ。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">目的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内容</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">目的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">テストケースの抜け漏れを機能横断で確認する</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">目的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ロール差異、外部連携、フォールバック、異常系の網羅状況を見える化する</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">目的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">実施前に、どの環境・どのアカウントで何を確認するかを固める</t>
-  </si>
-  <si>
-    <t xml:space="preserve">判定記号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">記号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">意味</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○</t>
-  </si>
-  <si>
-    <t xml:space="preserve">対応あり</t>
-  </si>
-  <si>
-    <t xml:space="preserve">△</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条件付きで対応あり</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">対象外</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">機能 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="游ゴシック体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">ロール</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">機能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPER</t>
   </si>
   <si>
     <t xml:space="preserve">ADMIN</t>
@@ -4285,7 +4044,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4408,22 +4167,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック体"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Microsoft Sans Serif"/>
@@ -4439,13 +4182,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="8"/>
       <name val="游ゴシック体"/>
       <family val="2"/>
       <charset val="1"/>
@@ -4644,7 +4381,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4725,39 +4462,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4789,7 +4506,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5493,6 +5210,9 @@
       <c r="E14" s="14" t="s">
         <v>64</v>
       </c>
+      <c r="F14" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
@@ -5510,6 +5230,9 @@
       <c r="E15" s="16" t="s">
         <v>68</v>
       </c>
+      <c r="F15" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
@@ -5527,6 +5250,9 @@
       <c r="E16" s="14" t="s">
         <v>71</v>
       </c>
+      <c r="F16" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
@@ -5544,6 +5270,9 @@
       <c r="E17" s="16" t="s">
         <v>74</v>
       </c>
+      <c r="F17" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
@@ -5561,6 +5290,9 @@
       <c r="E18" s="14" t="s">
         <v>77</v>
       </c>
+      <c r="F18" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
@@ -5578,6 +5310,9 @@
       <c r="E19" s="16" t="s">
         <v>81</v>
       </c>
+      <c r="F19" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
@@ -5595,6 +5330,9 @@
       <c r="E20" s="14" t="s">
         <v>84</v>
       </c>
+      <c r="F20" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
@@ -5612,6 +5350,9 @@
       <c r="E21" s="16" t="s">
         <v>87</v>
       </c>
+      <c r="F21" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
@@ -5629,6 +5370,9 @@
       <c r="E22" s="14" t="s">
         <v>91</v>
       </c>
+      <c r="F22" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
@@ -5646,6 +5390,9 @@
       <c r="E23" s="16" t="s">
         <v>94</v>
       </c>
+      <c r="F23" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
@@ -5663,6 +5410,9 @@
       <c r="E24" s="14" t="s">
         <v>97</v>
       </c>
+      <c r="F24" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
@@ -5680,6 +5430,9 @@
       <c r="E25" s="16" t="s">
         <v>100</v>
       </c>
+      <c r="F25" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
@@ -5697,6 +5450,9 @@
       <c r="E26" s="14" t="s">
         <v>103</v>
       </c>
+      <c r="F26" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
@@ -5714,6 +5470,9 @@
       <c r="E27" s="16" t="s">
         <v>106</v>
       </c>
+      <c r="F27" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
@@ -5730,6 +5489,9 @@
       </c>
       <c r="E28" s="14" t="s">
         <v>109</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6229,9 +5991,9 @@
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="7.4921875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="6.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="9" width="16.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="44.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="28"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="9" width="7.49"/>
@@ -6241,27 +6003,27 @@
       <c r="A1" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="19" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>211</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="14" t="s">
         <v>213</v>
       </c>
       <c r="D2" s="14"/>
@@ -6270,13 +6032,13 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>215</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="16" t="s">
         <v>217</v>
       </c>
       <c r="D3" s="16"/>
@@ -6285,13 +6047,13 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>219</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="14" t="s">
         <v>221</v>
       </c>
       <c r="D4" s="14"/>
@@ -6300,13 +6062,13 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="21" t="s">
         <v>222</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="16" t="s">
         <v>224</v>
       </c>
       <c r="D5" s="16"/>
@@ -6315,13 +6077,13 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>226</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="14" t="s">
         <v>228</v>
       </c>
       <c r="D6" s="14"/>
@@ -6330,13 +6092,13 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="21" t="s">
         <v>229</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="16" t="s">
         <v>231</v>
       </c>
       <c r="D7" s="16"/>
@@ -6345,13 +6107,13 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="20" t="s">
         <v>232</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="14" t="s">
         <v>234</v>
       </c>
       <c r="D8" s="14"/>
@@ -6360,7 +6122,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="21" t="s">
         <v>236</v>
       </c>
       <c r="B9" s="16" t="s">
@@ -6375,13 +6137,13 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="14" t="s">
         <v>242</v>
       </c>
       <c r="D10" s="14"/>
@@ -6390,7 +6152,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="21" t="s">
         <v>243</v>
       </c>
       <c r="B11" s="16" t="s">
@@ -6405,13 +6167,13 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>246</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="14" t="s">
         <v>248</v>
       </c>
       <c r="D12" s="14"/>
@@ -6420,7 +6182,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>249</v>
       </c>
       <c r="B13" s="16" t="s">
@@ -6435,13 +6197,13 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="20" t="s">
         <v>252</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="14" t="s">
         <v>254</v>
       </c>
       <c r="D14" s="14"/>
@@ -6450,13 +6212,13 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="21" t="s">
         <v>255</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="16" t="s">
         <v>257</v>
       </c>
       <c r="D15" s="16"/>
@@ -6465,13 +6227,13 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="20" t="s">
         <v>258</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="14" t="s">
         <v>260</v>
       </c>
       <c r="D16" s="14"/>
@@ -6480,13 +6242,13 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="21" t="s">
         <v>261</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="16" t="s">
         <v>263</v>
       </c>
       <c r="D17" s="16"/>
@@ -6495,13 +6257,13 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="14" t="s">
         <v>266</v>
       </c>
       <c r="D18" s="14"/>
@@ -6510,13 +6272,13 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="21" t="s">
         <v>267</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="16" t="s">
         <v>269</v>
       </c>
       <c r="D19" s="16"/>
@@ -6525,13 +6287,13 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="20" t="s">
         <v>270</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="14" t="s">
         <v>272</v>
       </c>
       <c r="D20" s="14"/>
@@ -6540,13 +6302,13 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="21" t="s">
         <v>273</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="16" t="s">
         <v>275</v>
       </c>
       <c r="D21" s="16"/>
@@ -6555,13 +6317,13 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="20" t="s">
         <v>276</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="14" t="s">
         <v>278</v>
       </c>
       <c r="D22" s="14"/>
@@ -6597,13 +6359,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="22" t="s">
         <v>281</v>
       </c>
     </row>
@@ -6722,1561 +6484,1648 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="2" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="2" width="24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="8.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="2" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="2" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="2" width="24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="2" width="8.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="24" t="s">
         <v>300</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="24" t="s">
         <v>301</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="B5" s="30"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="26" t="s">
         <v>303</v>
       </c>
+      <c r="C6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="28" t="s">
         <v>305</v>
       </c>
+      <c r="C7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="28.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="28" t="s">
         <v>307</v>
       </c>
+      <c r="C8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="28.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="27" t="s">
         <v>308</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="28" t="s">
         <v>309</v>
       </c>
+      <c r="C9" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="B11" s="30"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="26" t="s">
         <v>311</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="26" t="s">
         <v>312</v>
       </c>
+      <c r="C12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="B13" s="32" t="s">
+      <c r="A13" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="B13" s="27" t="s">
         <v>314</v>
       </c>
+      <c r="C13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="27" t="s">
         <v>316</v>
       </c>
+      <c r="C14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="s">
-        <v>317</v>
-      </c>
-      <c r="B15" s="32" t="s">
+      <c r="A15" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>318</v>
       </c>
+      <c r="C15" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="25" t="s">
         <v>319</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="26" t="s">
         <v>321</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="30" t="s">
         <v>327</v>
       </c>
+      <c r="I18" s="26" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="B19" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H19" s="34" t="s">
+      <c r="B19" s="27"/>
+      <c r="C19" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="B20" s="27"/>
+      <c r="C20" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I20" s="29" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="B21" s="27"/>
+      <c r="C21" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I21" s="29" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="27"/>
+      <c r="C22" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I23" s="29" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="B25" s="27"/>
+      <c r="C25" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="B29" s="27"/>
+      <c r="C29" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E29" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="B30" s="27"/>
+      <c r="C30" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="B31" s="27"/>
+      <c r="C31" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E31" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G31" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I31" s="29" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="B32" s="27"/>
+      <c r="C32" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="E32" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G32" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H32" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I32" s="29" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="B33" s="27"/>
+      <c r="C33" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F33" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G33" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H33" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="B34" s="29"/>
+      <c r="C34" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="E34" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="F34" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="G34" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="H34" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="I34" s="29" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="E35" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="G35" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="H35" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="I35" s="29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="B36" s="29"/>
+      <c r="C36" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E36" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="F36" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H36" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I36" s="29" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B37" s="27"/>
+      <c r="C37" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F37" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I37" s="29" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="E38" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F38" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G38" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H38" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I38" s="29" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="B39" s="27"/>
+      <c r="C39" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="E39" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F39" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H39" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I39" s="29" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="B40" s="27"/>
+      <c r="C40" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F40" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G40" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H40" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I40" s="29" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="27" t="s">
+        <v>356</v>
+      </c>
+      <c r="B41" s="27"/>
+      <c r="C41" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E41" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G41" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H41" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I41" s="29" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="25"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="26" t="s">
+        <v>359</v>
+      </c>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="G44" s="26" t="s">
+        <v>361</v>
+      </c>
+      <c r="H44" s="26" t="s">
+        <v>362</v>
+      </c>
+      <c r="I44" s="26" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H20" s="34" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="B21" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C21" s="38" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G45" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="H45" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I45" s="29" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E46" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F46" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G46" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H46" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I46" s="29" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="27" t="s">
+        <v>367</v>
+      </c>
+      <c r="B47" s="27"/>
+      <c r="C47" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E47" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="E21" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="B22" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E22" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H22" s="34" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="B23" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H23" s="34" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
-        <v>333</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H24" s="34" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D25" s="37" t="s">
+      <c r="F47" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G47" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="E25" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H25" s="34" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
-        <v>337</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E26" s="37" t="s">
+      <c r="H47" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I47" s="29" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="29" t="s">
+        <v>369</v>
+      </c>
+      <c r="B48" s="29"/>
+      <c r="C48" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D48" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="F26" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G26" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H26" s="34" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D27" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H27" s="34" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="B28" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H28" s="34" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="B29" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H29" s="34" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="B30" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="s">
-        <v>345</v>
-      </c>
-      <c r="B31" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H31" s="34" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32" t="s">
-        <v>347</v>
-      </c>
-      <c r="B32" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H32" s="34" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="32" t="s">
-        <v>256</v>
-      </c>
-      <c r="B33" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H33" s="34" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34" t="s">
-        <v>259</v>
-      </c>
-      <c r="B34" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C34" s="38" t="s">
+      <c r="E48" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F48" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G48" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H48" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I48" s="29" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="B49" s="27"/>
+      <c r="C49" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D49" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="E49" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G49" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H49" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="E34" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="H34" s="34" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34" t="s">
-        <v>262</v>
-      </c>
-      <c r="B35" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="H35" s="34" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34" t="s">
-        <v>350</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="E36" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F36" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H36" s="34" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="B37" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D37" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E37" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F37" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G37" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H37" s="34" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="B38" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C38" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="D38" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E38" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F38" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G38" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H38" s="34" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="B39" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C39" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E39" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G39" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H39" s="34" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="32" t="s">
-        <v>353</v>
-      </c>
-      <c r="B40" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C40" s="38" t="s">
-        <v>317</v>
-      </c>
-      <c r="D40" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E40" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F40" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G40" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H40" s="34" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="B41" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C41" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H41" s="34" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="30" t="s">
-        <v>357</v>
-      </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="D44" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="E44" s="31" t="s">
+      <c r="I49" s="29" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="F44" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="G44" s="31" t="s">
-        <v>361</v>
-      </c>
-      <c r="H44" s="31" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="32" t="s">
-        <v>362</v>
-      </c>
-      <c r="B45" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D45" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F45" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="G45" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H45" s="34" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="32" t="s">
-        <v>364</v>
-      </c>
-      <c r="B46" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C46" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F46" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G46" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H46" s="34" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="B47" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C47" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="G47" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H47" s="34" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="34" t="s">
-        <v>368</v>
-      </c>
-      <c r="B48" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C48" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="D48" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E48" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H48" s="34" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="32" t="s">
-        <v>370</v>
-      </c>
-      <c r="B49" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C49" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="D49" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F49" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G49" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="H49" s="34" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="30" t="s">
-        <v>372</v>
-      </c>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="B52" s="35" t="s">
-        <v>373</v>
-      </c>
-      <c r="C52" s="36" t="s">
+      <c r="B52" s="26"/>
+      <c r="C52" s="30" t="s">
         <v>374</v>
       </c>
       <c r="D52" s="31" t="s">
         <v>375</v>
       </c>
-      <c r="E52" s="35" t="s">
+      <c r="E52" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="F52" s="35" t="s">
+      <c r="F52" s="30" t="s">
         <v>377</v>
       </c>
-      <c r="G52" s="35" t="s">
+      <c r="G52" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="H52" s="35" t="s">
+      <c r="H52" s="30" t="s">
         <v>379</v>
       </c>
-      <c r="I52" s="31" t="s">
-        <v>327</v>
+      <c r="I52" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="J52" s="26" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="B53" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C53" s="38" t="s">
+      <c r="A53" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="B53" s="27"/>
+      <c r="C53" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D53" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="D53" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E53" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F53" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G53" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H53" s="39" t="s">
+      <c r="E53" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F53" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G53" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H53" s="34" t="s">
         <v>317</v>
       </c>
       <c r="I53" s="34" t="s">
-        <v>381</v>
+        <v>317</v>
+      </c>
+      <c r="J53" s="29" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="32" t="s">
-        <v>382</v>
-      </c>
-      <c r="B54" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C54" s="38" t="s">
+      <c r="A54" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="B54" s="27"/>
+      <c r="C54" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D54" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="D54" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E54" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F54" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G54" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H54" s="39" t="s">
+      <c r="E54" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F54" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G54" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H54" s="34" t="s">
         <v>317</v>
       </c>
       <c r="I54" s="34" t="s">
-        <v>365</v>
+        <v>317</v>
+      </c>
+      <c r="J54" s="29" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="32" t="s">
-        <v>383</v>
-      </c>
-      <c r="B55" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C55" s="38" t="s">
+      <c r="A55" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="B55" s="27"/>
+      <c r="C55" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D55" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="D55" s="37" t="s">
+      <c r="E55" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="E55" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F55" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G55" s="37" t="s">
+      <c r="F55" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G55" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H55" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="H55" s="39" t="s">
-        <v>317</v>
-      </c>
       <c r="I55" s="34" t="s">
-        <v>367</v>
+        <v>317</v>
+      </c>
+      <c r="J55" s="29" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="B56" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C56" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D56" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E56" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F56" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G56" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="I56" s="34" t="s">
+      <c r="A56" s="29" t="s">
         <v>341</v>
       </c>
+      <c r="B56" s="29"/>
+      <c r="C56" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E56" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F56" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G56" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H56" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I56" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="J56" s="29" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="B57" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C57" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D57" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E57" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F57" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G57" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H57" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="I57" s="34" t="s">
+      <c r="A57" s="27" t="s">
         <v>343</v>
       </c>
+      <c r="B57" s="27"/>
+      <c r="C57" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F57" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G57" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H57" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I57" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="J57" s="29" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="B58" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C58" s="38" t="s">
+      <c r="A58" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="B58" s="27"/>
+      <c r="C58" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D58" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="D58" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E58" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F58" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G58" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H58" s="39" t="s">
+      <c r="E58" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F58" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G58" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H58" s="34" t="s">
         <v>317</v>
       </c>
       <c r="I58" s="34" t="s">
-        <v>385</v>
+        <v>317</v>
+      </c>
+      <c r="J58" s="29" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="34" t="s">
-        <v>386</v>
-      </c>
-      <c r="B59" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="D59" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F59" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G59" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H59" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="I59" s="34" t="s">
-        <v>349</v>
+      <c r="A59" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="B59" s="29"/>
+      <c r="C59" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D59" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E59" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F59" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G59" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H59" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I59" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="J59" s="29" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="34" t="s">
-        <v>387</v>
-      </c>
-      <c r="B60" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C60" s="38" t="s">
+      <c r="A60" s="29" t="s">
+        <v>388</v>
+      </c>
+      <c r="B60" s="29"/>
+      <c r="C60" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D60" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="D60" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="E60" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F60" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G60" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H60" s="37" t="s">
+      <c r="E60" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G60" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H60" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="I60" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="I60" s="34" t="s">
+      <c r="J60" s="29" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="34" t="s">
-        <v>388</v>
-      </c>
-      <c r="B61" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C61" s="38" t="s">
+      <c r="A61" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="B61" s="29"/>
+      <c r="C61" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D61" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="D61" s="37" t="s">
+      <c r="E61" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="E61" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="F61" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G61" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H61" s="37" t="s">
+      <c r="F61" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="G61" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H61" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="I61" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="I61" s="34" t="s">
-        <v>351</v>
+      <c r="J61" s="29" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="32" t="s">
-        <v>389</v>
-      </c>
-      <c r="B62" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="C62" s="38" t="s">
+      <c r="A62" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="B62" s="27"/>
+      <c r="C62" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D62" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="D62" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="E62" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="F62" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="G62" s="39" t="s">
-        <v>317</v>
-      </c>
-      <c r="H62" s="39" t="s">
+      <c r="E62" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F62" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G62" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H62" s="34" t="s">
         <v>317</v>
       </c>
       <c r="I62" s="34" t="s">
-        <v>390</v>
+        <v>317</v>
+      </c>
+      <c r="J62" s="29" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="30" t="s">
-        <v>391</v>
-      </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
+      <c r="A64" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="31" t="s">
-        <v>392</v>
-      </c>
-      <c r="B65" s="31" t="s">
+      <c r="A65" s="26" t="s">
         <v>393</v>
       </c>
-      <c r="C65" s="36" t="s">
+      <c r="B65" s="26"/>
+      <c r="C65" s="26" t="s">
         <v>394</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>327</v>
+        <v>395</v>
+      </c>
+      <c r="E65" s="26" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="34" t="s">
-        <v>321</v>
-      </c>
-      <c r="B66" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="C66" s="38" t="s">
+      <c r="A66" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="B66" s="29"/>
+      <c r="C66" s="33" t="s">
         <v>396</v>
       </c>
       <c r="D66" s="33" t="s">
         <v>397</v>
       </c>
+      <c r="E66" s="28" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="34" t="s">
-        <v>322</v>
-      </c>
-      <c r="B67" s="38" t="s">
-        <v>398</v>
-      </c>
-      <c r="C67" s="38" t="s">
+      <c r="A67" s="29" t="s">
+        <v>323</v>
+      </c>
+      <c r="B67" s="29"/>
+      <c r="C67" s="33" t="s">
         <v>399</v>
       </c>
       <c r="D67" s="33" t="s">
         <v>400</v>
       </c>
+      <c r="E67" s="28" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="28.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="34" t="s">
-        <v>323</v>
-      </c>
-      <c r="B68" s="38" t="s">
-        <v>401</v>
-      </c>
-      <c r="C68" s="38" t="s">
+      <c r="A68" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="B68" s="29"/>
+      <c r="C68" s="33" t="s">
         <v>402</v>
       </c>
       <c r="D68" s="33" t="s">
         <v>403</v>
       </c>
+      <c r="E68" s="28" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="28.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="34" t="s">
-        <v>324</v>
-      </c>
-      <c r="B69" s="38" t="s">
-        <v>404</v>
-      </c>
-      <c r="C69" s="38" t="s">
+      <c r="A69" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="B69" s="29"/>
+      <c r="C69" s="33" t="s">
         <v>405</v>
       </c>
       <c r="D69" s="33" t="s">
         <v>406</v>
       </c>
+      <c r="E69" s="28" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="19.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="B70" s="38" t="s">
-        <v>407</v>
-      </c>
-      <c r="C70" s="38" t="s">
+      <c r="A70" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="B70" s="29"/>
+      <c r="C70" s="33" t="s">
         <v>408</v>
       </c>
       <c r="D70" s="33" t="s">
         <v>409</v>
       </c>
+      <c r="E70" s="28" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="19.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="34" t="s">
-        <v>326</v>
-      </c>
-      <c r="B71" s="38" t="s">
-        <v>410</v>
-      </c>
-      <c r="C71" s="38" t="s">
+      <c r="A71" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="B71" s="29"/>
+      <c r="C71" s="33" t="s">
         <v>411</v>
       </c>
       <c r="D71" s="33" t="s">
         <v>412</v>
       </c>
+      <c r="E71" s="28" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="B73" s="30"/>
-      <c r="C73" s="30"/>
+      <c r="A73" s="25" t="s">
+        <v>414</v>
+      </c>
+      <c r="B73" s="25"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="31" t="s">
-        <v>414</v>
-      </c>
-      <c r="B74" s="31" t="s">
+      <c r="A74" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="C74" s="36" t="s">
+      <c r="B74" s="26"/>
+      <c r="C74" s="26" t="s">
         <v>416</v>
       </c>
+      <c r="D74" s="31" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="33" t="s">
-        <v>417</v>
-      </c>
-      <c r="B75" s="38" t="s">
+      <c r="A75" s="28" t="s">
         <v>418</v>
       </c>
+      <c r="B75" s="28"/>
       <c r="C75" s="33" t="s">
         <v>419</v>
       </c>
+      <c r="D75" s="28" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="33" t="s">
-        <v>420</v>
-      </c>
-      <c r="B76" s="38" t="s">
+      <c r="A76" s="28" t="s">
         <v>421</v>
       </c>
+      <c r="B76" s="28"/>
       <c r="C76" s="33" t="s">
         <v>422</v>
       </c>
+      <c r="D76" s="28" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="33" t="s">
-        <v>423</v>
-      </c>
-      <c r="B77" s="38" t="s">
+      <c r="A77" s="28" t="s">
         <v>424</v>
       </c>
+      <c r="B77" s="28"/>
       <c r="C77" s="33" t="s">
         <v>425</v>
       </c>
+      <c r="D77" s="28" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="33" t="s">
-        <v>426</v>
-      </c>
-      <c r="B78" s="38" t="s">
+      <c r="A78" s="28" t="s">
         <v>427</v>
       </c>
+      <c r="B78" s="28"/>
       <c r="C78" s="33" t="s">
         <v>428</v>
       </c>
+      <c r="D78" s="28" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="33" t="s">
-        <v>429</v>
-      </c>
-      <c r="B79" s="38" t="s">
+      <c r="A79" s="28" t="s">
         <v>430</v>
       </c>
+      <c r="B79" s="28"/>
       <c r="C79" s="33" t="s">
         <v>431</v>
       </c>
+      <c r="D79" s="28" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="B81" s="30"/>
+      <c r="A81" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="31" t="s">
-        <v>433</v>
-      </c>
-      <c r="B82" s="31" t="s">
+      <c r="A82" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="34" t="s">
-        <v>434</v>
-      </c>
-      <c r="B83" s="33" t="s">
+      <c r="A83" s="29" t="s">
         <v>435</v>
       </c>
+      <c r="B83" s="29"/>
+      <c r="C83" s="28" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="19.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="34" t="s">
-        <v>436</v>
-      </c>
-      <c r="B84" s="33" t="s">
+      <c r="A84" s="29" t="s">
         <v>437</v>
       </c>
+      <c r="B84" s="29"/>
+      <c r="C84" s="28" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="B85" s="33" t="s">
+      <c r="A85" s="29" t="s">
         <v>439</v>
       </c>
+      <c r="B85" s="29"/>
+      <c r="C85" s="28" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="19.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="34" t="s">
-        <v>440</v>
-      </c>
-      <c r="B86" s="33" t="s">
+      <c r="A86" s="29" t="s">
         <v>441</v>
       </c>
+      <c r="B86" s="29"/>
+      <c r="C86" s="28" t="s">
+        <v>442</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="20.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="34" t="s">
-        <v>442</v>
-      </c>
-      <c r="B87" s="33" t="s">
+      <c r="A87" s="29" t="s">
         <v>443</v>
       </c>
+      <c r="B87" s="29"/>
+      <c r="C87" s="28" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="34" t="s">
-        <v>444</v>
-      </c>
-      <c r="B88" s="33" t="s">
+      <c r="A88" s="29" t="s">
         <v>445</v>
       </c>
+      <c r="B88" s="29"/>
+      <c r="C88" s="28" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="30" t="s">
-        <v>446</v>
-      </c>
-      <c r="B90" s="30"/>
+      <c r="A90" s="25" t="s">
+        <v>447</v>
+      </c>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="31" t="s">
+      <c r="A91" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="B91" s="31" t="s">
+      <c r="B91" s="26"/>
+      <c r="C91" s="26" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="29.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="33" t="s">
-        <v>447</v>
-      </c>
-      <c r="B92" s="33" t="s">
+      <c r="A92" s="28" t="s">
         <v>448</v>
       </c>
+      <c r="B92" s="28"/>
+      <c r="C92" s="28" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="20.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="33" t="s">
-        <v>449</v>
-      </c>
-      <c r="B93" s="33" t="s">
+      <c r="A93" s="28" t="s">
         <v>450</v>
       </c>
+      <c r="B93" s="28"/>
+      <c r="C93" s="28" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="37.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="33" t="s">
-        <v>451</v>
-      </c>
-      <c r="B94" s="33" t="s">
+      <c r="A94" s="28" t="s">
         <v>452</v>
+      </c>
+      <c r="B94" s="28"/>
+      <c r="C94" s="28" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A51:I51"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A90:C90"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
